--- a/docs/test-suite/MedERP_Test_Suite_updated.xlsx
+++ b/docs/test-suite/MedERP_Test_Suite_updated.xlsx
@@ -41,10 +41,10 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'TS-04'!$A$4:$P$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'TS-05'!$A$4:$P$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'TS-06'!$A$4:$P$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'TS-07'!$A$4:$P$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'TS-07'!$A$4:$P$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'TS-08'!$A$4:$P$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'TS-09'!$A$4:$P$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'TS-10'!$A$4:$P$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'TS-10'!$A$4:$P$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'TS-11'!$A$4:$P$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'TS-12'!$A$4:$P$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'TS-13'!$A$4:$P$24</definedName>
@@ -891,11 +891,11 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Branding, OPD fee, signature &amp; walk-in policy, admin-as-doctor, view-mode</t>
+          <t>Branding, OPD fee, policies, admin-as-doctor, doctor availability (Everyday/Weekdays/Weekend)</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>18 cases written</t>
+          <t>26 cases written</t>
         </is>
       </c>
     </row>
@@ -1017,11 +1017,11 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Booking, walk-in, token, status machine, reschedule, no-show, remind</t>
+          <t>Booking, walk-in, token, status machine, reschedule, doctor availability slots</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>42 cases written</t>
+          <t>52 cases written</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P22"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1532,7 +1532,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 18 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 26 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -2811,14 +2811,553 @@
       </c>
       <c r="P22" s="4" t="inlineStr"/>
     </row>
+    <row r="23" ht="60" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-019</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Doctor Hours</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Settings shows Doctor availability hours section</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>At least one active DOCTOR staff.</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>/hospital/settings</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>1. Scroll to Doctor availability hours.
+2. Confirm each active doctor has an editor.
+3. Open day dropdown.</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>Section visible. Day options include Everyday, Weekdays, Weekend, and each single day.</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr"/>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>/hospital/settings</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24" ht="60" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-020</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Doctor Hours</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Save multiple windows same day (morning/afternoon/evening)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Active doctor D1.</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Mon 10:00–12:00, 14:00–16:00, 18:00–20:00</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>1. Add three Monday windows.
+2. Save availability.</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>Saved. Audit DOCTOR_AVAILABILITY_UPDATED. GET returns 3 windows.</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>PUT /api/hospital/staff/[id]/availability</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-021</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Doctor Hours</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Overlapping windows on same day rejected</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Doctor D1.</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Mon 10:00–13:00 and 12:00–14:00</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>1. Save overlapping windows.</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>400 with overlap error. Previous windows unchanged.</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>PUT availability</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-022</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Doctor Hours</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>End time must be after start time</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Doctor D1.</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Tue start 16:00 end 10:00</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>1. Save.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>400 End time must be after start time.</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>PUT availability</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-023</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Doctor Hours</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Weekdays preset expands to Mon–Fri</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Active doctor D1.</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Day = Weekdays (Mon–Fri), 10:00–13:00</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>1. Add window → Weekdays → 10:00–13:00.
+2. Save.
+3. GET availability.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Saved as 5 windows (Mon–Fri same band). Reload shows Weekdays row collapsed.</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>PUT/GET /api/hospital/staff/[id]/availability</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28" ht="60" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-024</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Doctor Hours</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Weekend preset expands to Sat–Sun</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Active doctor D1.</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Day = Weekend (Sat–Sun), 10:00–12:00</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>1. Add Weekend window 10:00–12:00.
+2. Save.
+3. GET.</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>2 windows (Saturday + Sunday). Reload shows Weekend row.</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>PUT/GET availability</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-025</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Doctor Hours</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Everyday preset expands to all 7 days</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Active doctor D1.</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Day = Everyday (Sun–Sat), 09:00–17:00</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>1. Add Everyday window.
+2. Save.
+3. GET.</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>7 windows (Sun–Sat). Reload collapses to Everyday row.</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>PUT/GET availability</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-026</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Doctor Hours</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Different doctors have independent schedules</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Active doctors D1 and D2.</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>D1 Weekdays 10–13; D2 Weekend 10–12</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>1. Save D1 Weekdays 10:00–13:00.
+2. Save D2 Weekend 10:00–12:00.
+3. GET both.</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>D1 has Mon–Fri only. D2 has Sat–Sun only. No cross-contamination.</t>
+        </is>
+      </c>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>PUT/GET availability per staff id</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P22"/>
+  <autoFilter ref="A4:P30"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6947,7 +7486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6978,7 +7517,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 42 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 52 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -9839,14 +10378,678 @@
       </c>
       <c r="P46" s="4" t="inlineStr"/>
     </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-043</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Booking form shows slot list when doctor has windows</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Doctor D1 has Mon 10:00–12:00 and 14:00–16:00.</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Date = next Monday</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>1. /appointments/new → select D1 → pick Monday.
+2. Open Available time.</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Dropdown shows 15-min slots inside windows only (not 13:00).</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr"/>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/appointments/availability</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-044</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Cannot book outside configured windows</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Doctor D1 Mon 10:00–12:00 only.</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>scheduledAt Monday 15:00</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>1. POST appointment outside window (API or UI).</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>400 Chosen time is outside the doctor's availability.</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/appointments</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49" ht="60" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-045</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Book inside window succeeds</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Doctor D1 Mon 10:00–12:00.</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Monday 10:30</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>1. Book scheduled appointment.</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>201 SCHEDULED. Token issued.</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr"/>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/appointments</t>
+        </is>
+      </c>
+      <c r="P49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50" ht="60" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-046</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Day with no windows shows empty slots / cannot book</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Doctor D1 only Monday windows.</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Date = Tuesday</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>1. Select D1 + Tuesday.</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>No slots / message no availability. POST 400 if forced.</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>availability + POST</t>
+        </is>
+      </c>
+      <c r="P50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51" ht="60" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-047</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>No windows configured — free-form time still allowed</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Doctor D2 has zero StaffAvailabilityWindow rows.</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Any datetime-local</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>1. Book any future time.</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>Allowed (legacy). UI shows free time input.</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr"/>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/appointments</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr"/>
+    </row>
+    <row r="52" ht="60" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-048</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Reschedule outside window rejected</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Appt for D1 inside window. D1 Mon 10–12 only.</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Reschedule to Monday 15:00</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>1. action=reschedule.</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>400 outside availability.</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>PATCH appointments/[id]</t>
+        </is>
+      </c>
+      <c r="P52" s="4" t="inlineStr"/>
+    </row>
+    <row r="53" ht="60" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-049</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Weekdays schedule offers slots Mon–Fri only</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Doctor D1 saved Weekdays 10:00–13:00.</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Next Wednesday and next Saturday</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>1. Select D1 + Wednesday → slots 10:00–12:45.
+2. Select D1 + Saturday.</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>Wednesday has slots. Saturday has no slots / cannot book.</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr"/>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M53" s="4" t="inlineStr"/>
+      <c r="N53" s="4" t="inlineStr"/>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/appointments/availability</t>
+        </is>
+      </c>
+      <c r="P53" s="4" t="inlineStr"/>
+    </row>
+    <row r="54" ht="60" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-050</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Weekend schedule offers slots Sat–Sun only</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Doctor D1 saved Weekend 10:00–12:00.</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Next Saturday and next Monday</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>1. Book Saturday 10:30 (ok).
+2. Attempt Monday 10:30.</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>Saturday succeeds. Monday 400 / no slots.</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr"/>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M54" s="4" t="inlineStr"/>
+      <c r="N54" s="4" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>availability + POST</t>
+        </is>
+      </c>
+      <c r="P54" s="4" t="inlineStr"/>
+    </row>
+    <row r="55" ht="60" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-051</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Everyday schedule offers slots any day of week</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Doctor D1 saved Everyday 09:00–17:00.</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Next Sunday and next Wednesday</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>1. Check slots both days inside 09–17.</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>Both days show slots. Book either succeeds.</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr"/>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M55" s="4" t="inlineStr"/>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>GET availability + POST</t>
+        </is>
+      </c>
+      <c r="P55" s="4" t="inlineStr"/>
+    </row>
+    <row r="56" ht="60" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-052</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Availability</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Switching doctor reloads that doctor's slots only</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>D1 Weekdays 10–13; D2 Weekend 10–12.</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Date = next Saturday</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>1. Select D1 + Saturday → no slots.
+2. Switch to D2 + same Saturday.</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>D2 shows weekend slots. Times never mix across doctors.</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr"/>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M56" s="4" t="inlineStr"/>
+      <c r="N56" s="4" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/appointments/availability?doctorId=</t>
+        </is>
+      </c>
+      <c r="P56" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P46"/>
+  <autoFilter ref="A4:P56"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L67" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29133,7 +30336,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>/api/hospital/settings, /api/hospital/doctor-profile, /api/session/view-mode</t>
+          <t>/api/hospital/settings, /api/hospital/doctor-profile, /api/hospital/staff/[id]/availability, /api/session/view-mode</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">

--- a/docs/test-suite/MedERP_Test_Suite_updated.xlsx
+++ b/docs/test-suite/MedERP_Test_Suite_updated.xlsx
@@ -38,23 +38,23 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TS-01'!$A$4:$P$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TS-02'!$A$4:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'TS-03'!$A$4:$P$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'TS-04'!$A$4:$P$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'TS-05'!$A$4:$P$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'TS-06'!$A$4:$P$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'TS-07'!$A$4:$P$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'TS-08'!$A$4:$P$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'TS-09'!$A$4:$P$42</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'TS-10'!$A$4:$P$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'TS-04'!$A$4:$P$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'TS-05'!$A$4:$P$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'TS-06'!$A$4:$P$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'TS-07'!$A$4:$P$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'TS-08'!$A$4:$P$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'TS-09'!$A$4:$P$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'TS-10'!$A$4:$P$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'TS-11'!$A$4:$P$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="14" hidden="1">'TS-12'!$A$4:$P$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'TS-13'!$A$4:$P$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'TS-14'!$A$4:$P$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'TS-14'!$A$4:$P$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="17" hidden="1">'TS-15'!$A$4:$P$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'TS-16'!$A$4:$P$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="18" hidden="1">'TS-16'!$A$4:$P$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TS-17'!$A$4:$P$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TS-18'!$A$4:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="21" hidden="1">'TS-19'!$A$4:$P$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TS-20'!$A$4:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="22" hidden="1">'TS-20'!$A$4:$P$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -765,11 +765,11 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Tiers, seats, module gating, trial expiry, tier change, webhooks</t>
+          <t>Tiers, seats, module gating, trial expiry, tier change, webhooks, monthly subscription bill WhatsApp to SUPER_ADMIN</t>
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>20 cases written</t>
+          <t>23 cases written</t>
         </is>
       </c>
     </row>
@@ -807,11 +807,11 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Hospital CRUD, stop access, platform users, invoices, billing settings</t>
+          <t>Hospital CRUD, stop access, platform users, invoices, billing settings on every subscription bill</t>
         </is>
       </c>
       <c r="D9" s="4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
@@ -832,7 +832,7 @@
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>24 cases written</t>
+          <t>25 cases written</t>
         </is>
       </c>
     </row>
@@ -849,11 +849,11 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Create/edit staff, codes, seats, deactivate, signatures, merge</t>
+          <t>Create/edit staff, codes, seats, deactivate, signatures, merge; Receptionist + Nurse both remain available</t>
         </is>
       </c>
       <c r="D10" s="4" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -874,7 +874,7 @@
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>34 cases written</t>
+          <t>36 cases written</t>
         </is>
       </c>
     </row>
@@ -891,11 +891,11 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Branding, OPD fee, policies, admin-as-doctor, doctor availability (Everyday/Weekdays/Weekend)</t>
+          <t>Branding, OPD fee, walk-in policy, nurses as receptionists, admin-as-doctor, doctor availability</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>26 cases written</t>
+          <t>34 cases written</t>
         </is>
       </c>
     </row>
@@ -933,11 +933,11 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Apply/approve/reject/cancel, overlap, doctor availability impact</t>
+          <t>Apply/approve/reject/cancel, overlap, doctor availability impact; nurse record-leave when opted in</t>
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
@@ -958,7 +958,7 @@
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>20 cases written</t>
+          <t>22 cases written</t>
         </is>
       </c>
     </row>
@@ -975,11 +975,11 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Register, UHID, duplicates, family, merge, search, edit permissions</t>
+          <t>Register, UHID, unnamed infant Baby of parent, duplicates, family, merge, search, edit permissions; nurse-as-receptionist register/edit</t>
         </is>
       </c>
       <c r="D13" s="4" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>38 cases written</t>
+          <t>44 cases written</t>
         </is>
       </c>
     </row>
@@ -1017,11 +1017,11 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Booking, walk-in, token, status machine, reschedule, doctor availability slots</t>
+          <t>Booking, walk-in, token, status machine, reschedule, doctor availability slots; nurse front desk when opted in</t>
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>52 cases written</t>
+          <t>56 cases written</t>
         </is>
       </c>
     </row>
@@ -1185,11 +1185,11 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Invoice numbering, line math, OPD collect, card brand</t>
+          <t>Invoice numbering, line math, OPD collect, card brand; nurse billing when opted in</t>
         </is>
       </c>
       <c r="D18" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>28 cases written</t>
+          <t>30 cases written</t>
         </is>
       </c>
     </row>
@@ -1269,11 +1269,11 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Daily collections, monthly report, CSV, outstanding, WhatsApp receipt</t>
+          <t>Daily collections, monthly report, CSV, outstanding, WhatsApp receipt; nurse reports when opted in</t>
         </is>
       </c>
       <c r="D20" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>22 cases written</t>
+          <t>23 cases written</t>
         </is>
       </c>
     </row>
@@ -1437,11 +1437,11 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Role × module negative matrix, cross-hospital access attempts</t>
+          <t>Role × module negative matrix, cross-hospital access attempts, nurse-as-receptionist matrix</t>
         </is>
       </c>
       <c r="D24" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>30 cases written</t>
+          <t>32 cases written</t>
         </is>
       </c>
     </row>
@@ -1501,7 +1501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1532,7 +1532,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 26 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 34 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Enable walkInByNurse — nurse can walk-in</t>
+          <t>Enable walkInByNurse — nurse can walk-in (narrow toggle)</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>walkInByNurse true.</t>
+          <t>walkInByNurse true. nurseAsReceptionist false.</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Allowed.</t>
+          <t>Allowed. Nurse still cannot open billing / edit patient demographics (that needs Nurses as receptionists).</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr"/>
@@ -3350,14 +3350,551 @@
       </c>
       <c r="P30" s="4" t="inlineStr"/>
     </row>
+    <row r="31" ht="60" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-027</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Toggle default OFF — nurses stay off the front desk</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>H1. U-H1-NUR exists. nurseAsReceptionist never enabled (default false).</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>/patients/new, /billing, queue manage</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as nurse.
+2. Open /patients/new, /billing, try cancel/reschedule a visit.</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>Register/edit patient denied. Billing redirected/denied. Queue manage actions denied. Nurse station still available.</t>
+        </is>
+      </c>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>hasFrontDeskAccess / hasBillingAccess</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-028</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN enables Nurses as receptionists</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Logged in as U-H1-SUPER.</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist: true</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>1. Open /hospital/settings.
+2. Tick Nurses can do receptionist work.
+3. Save nurse reception access.</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>PATCH 200. Audit HOSPITAL_NURSE_RECEPTIONIST_POLICY_UPDATED. Dedicated Receptionist role is still available on Hospital users.</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /api/hospital/settings</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-029</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Non-admin cannot change the nurse receptionist toggle</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Toggle currently true or false.</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST / NURSE</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>PATCH nurseAsReceptionist</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>1. Call PATCH /api/hospital/settings with nurseAsReceptionist.</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>403 Hospital admin access required. Flag unchanged.</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /api/hospital/settings</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-030</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Toggle ON — every nurse gets front desk; receptionist still works</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist true. U-H1-NUR, U-H1-NUR2, U-H1-REC exist.</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>NURSE / RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as U-H1-NUR: register patient, add walk-in, open /billing.
+2. Repeat as U-H1-NUR2.
+3. Login as U-H1-REC: same front-desk actions still work.</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Both nurses can register, walk-in, collect. Receptionist unchanged. Nav for nurses includes Billing plus Nurse station.</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>hasFrontDeskAccess + nav</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-031</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Toggle ON implies walk-in even if walkInByNurse is off</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist true. walkInByNurse false.</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>WALK_IN</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>1. Confirm walk-in-by-nurse checkbox is disabled/checked in settings.
+2. Nurse creates walk-in.</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Walk-in allowed. Settings copy explains nurses already cover reception.</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>canAddWalkIn</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-032</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Toggle OFF restores nurse-only (does not remove Receptionist users)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Toggle was ON. U-H1-REC still exists.</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN → NURSE / RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist: false</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>1. Superadmin unchecks and saves.
+2. Login nurse — retry register/billing.
+3. Login receptionist — retry billing.</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Audit HOSPITAL_NURSE_RECEPTIONIST_POLICY_UPDATED. Nurse denied front desk again. Receptionist still has full front desk. Nurse user rows unchanged.</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /api/hospital/settings</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-033</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Empty PATCH / missing field rejected; branding still independent</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN.</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>body {}</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>1. PATCH settings with empty body.</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>400 Nothing to update. Existing nurseAsReceptionist unchanged.</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr"/>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /api/hospital/settings</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38" ht="60" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>TS-07-034</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Only one SUPER_ADMIN; admin-as-doctor remains that one admin</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>H1 has one SUPER_ADMIN. Toggle on or off.</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Hospital users + settings</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>1. Confirm hospital UI cannot create a second SUPER_ADMIN.
+2. Confirm admin-as-doctor still uses the same admin (TS-07-010).</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Staff roles only (including Receptionist and multiple Nurses). One hospital admin. Unrelated to nurse receptionist toggle.</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>TS-06-009 + doctor-profile</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P30"/>
+  <autoFilter ref="A4:P38"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3371,7 +3908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3402,7 +3939,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 20 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 22 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -4811,14 +5348,146 @@
       </c>
       <c r="P24" s="4" t="inlineStr"/>
     </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>TS-08-021</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Record RBAC</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Nurse cannot record leave when receptionist toggle is off</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist false.</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>record=true</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>1. POST /api/leaves with record=true.</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>403 Only reception or super admin can record leave directly.</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/leaves</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>TS-08-022</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Record RBAC</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Nurse can record leave when Nurses as receptionists is on</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist true (TS-07-028). No overlap.</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>record=true type CASUAL dates</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>1. Record leave for a doctor from appointments leave form or API.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Created APPROVED. Same as receptionist record path.</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/leaves</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P24"/>
+  <autoFilter ref="A4:P26"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4832,7 +5501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4863,7 +5532,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 38 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 44 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -5043,7 +5712,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>canRegisterPatient true.</t>
+          <t>canRegisterPatient true. nurseAsReceptionist false.</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -5063,7 +5732,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Form available.</t>
+          <t>Form available. Nurse cannot open /patients/new on default (see TS-09-039).</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -5164,7 +5833,7 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>firstName, dateOfBirth, gender required</t>
+          <t>firstName, dateOfBirth, gender required (unless unnamed infant)</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -5189,7 +5858,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Omit each required field in turn</t>
+          <t>Omit each required field in turn. unnamedInfant false.</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -5199,7 +5868,7 @@
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>400 validation for each missing required.</t>
+          <t>400 'First name and date of birth are required.' Gender still required. Unnamed infant path is TS-09-042.</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr"/>
@@ -5526,12 +6195,12 @@
       <c r="I13" s="4" t="inlineStr">
         <is>
           <t>1. Register P3.
-2. View detail.</t>
+2. View list + detail.</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Age displays as 'N M' months not years.</t>
+          <t>Age displays as 'N M' months (ageLabel), not years, on /patients and patient detail.</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr"/>
@@ -5544,7 +6213,7 @@
       <c r="N13" s="4" t="inlineStr"/>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>patient detail UI</t>
+          <t>patient list + detail UI</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr"/>
@@ -6355,7 +7024,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Edit page front desk only</t>
+          <t>Edit page front desk only (nurse denied by default)</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -6370,7 +7039,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nurseAsReceptionist false.</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -6390,7 +7059,7 @@
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Denied.</t>
+          <t>Denied / redirect to /patients.</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr"/>
@@ -7465,14 +8134,421 @@
       </c>
       <c r="P42" s="4" t="inlineStr"/>
     </row>
+    <row r="43" ht="60" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>TS-09-039</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist Off</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Nurse cannot register patient when toggle is off</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist false. walkInByNurse false.</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>/patients/new + POST /api/patients</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>1. Open /patients/new.
+2. POST register.</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Page redirects. API 403. List still visible (clinical view).</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr"/>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr"/>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>canRegisterPatient</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44" ht="60" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>TS-09-040</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist On</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Nurse can register, edit, family-link, merge when toggle is on</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist true (TS-07-028). Unused patient data.</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>New patient + edit address + family link</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>1. Register patient.
+2. Edit demographics.
+3. Link family if second patient exists.</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>All succeed like receptionist. Edit column appears on /patients list.</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr"/>
+      <c r="N44" s="4" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>POST/PATCH patients + family</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45" ht="60" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>TS-09-041</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist On</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Second nurse can also register (not one designated nurse)</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Toggle ON. U-H1-NUR2 exists (TS-06-036).</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>NURSE (U-H1-NUR2)</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Another unused patient</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>1. Login as second nurse.
+2. Register patient.</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Succeeds. Hospital-wide toggle — every nurse, not a single assignee.</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr"/>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr"/>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/patients</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46" ht="72" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>TS-09-042</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Infant</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Unnamed infant registers as Baby of parent without a given name</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Front desk. Parent name known. Extra sections stay collapsed.</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>unnamedInfant=true parentName='Ramesh Kumar' gender=MALE (DOB optional → today)</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>1. Open /patients/new.
+2. Tick Unnamed infant / newborn.
+3. Enter parent name + gender (and parent mobile if known).
+4. Save without filling first name or extra sections.</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Created firstName='Baby of Ramesh Kumar', lastName empty, DOB today if omitted. Audit PATIENT_REGISTERED. List/detail show that name. Fast path — no photo/history/ID required.</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/patients unnamedInfant</t>
+        </is>
+      </c>
+      <c r="P46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47" ht="60" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>TS-09-043</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Infant</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>Baby of name is easy to replace with the given name later</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Infant from TS-09-042 exists.</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>PATCH firstName=Aarav lastName=Kumar</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>1. Open Edit on the infant.
+2. Change Given name (banner explains Baby of).
+3. Save. Do not open extra sections.</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Name updates. UHID unchanged. Edit banner shown when firstName starts with Baby of.</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr"/>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /api/patients/[id]</t>
+        </is>
+      </c>
+      <c r="P47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48" ht="60" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>TS-09-044</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Infant Family</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Unnamed infant under existing parent uses parent record name</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Parent P1 on file with mobile.</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Parent mobile + unnamedInfant + familyOf P1</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter parent mobile (family lookup appears).
+2. Tick unnamed infant.
+3. Save as child under P1.</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>firstName=Baby of {P1 full name}. Inherits phone. PatientFamily CHILD. No 409 for shared phone. Same result from patient detail Add family member.</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/patients familyOf + unnamedInfant</t>
+        </is>
+      </c>
+      <c r="P48" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P42"/>
+  <autoFilter ref="A4:P48"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L63" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L69" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7486,7 +8562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P56"/>
+  <dimension ref="A1:P60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7517,7 +8593,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 52 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 56 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -10127,7 +11203,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Nurse walk-in denied when walkInByNurse false</t>
+          <t>Nurse walk-in denied when walkInByNurse false and receptionist toggle off</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
@@ -10142,7 +11218,7 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Policy false.</t>
+          <t>walkInByNurse false. nurseAsReceptionist false.</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -11042,14 +12118,285 @@
       </c>
       <c r="P56" s="4" t="inlineStr"/>
     </row>
+    <row r="57" ht="60" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-053</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Front Desk Off</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Nurse cannot cancel/reschedule/check-in when toggle is off</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist false. SCHEDULED visit exists.</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>cancel / reschedule / checkin</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>1. Attempt each front-desk action.</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>403. Nurse station / vitals still allowed (TS-11).</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr"/>
+      <c r="N57" s="4" t="inlineStr"/>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>appointments status/reschedule</t>
+        </is>
+      </c>
+      <c r="P57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58" ht="90" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-054</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Front Desk On</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Nurse can book, walk-in, check-in, cancel, reschedule when toggle is on</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist true. Patient + doctor available.</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>SCHEDULED then WALK_IN</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>1. Book scheduled.
+2. Walk-in.
+3. Check-in scheduled.
+4. Cancel one visit.
+5. Reschedule another.</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>All succeed like receptionist. Nurse still cannot start consult (W-01 / doctorOwnsVisit).</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>POST appointments + status</t>
+        </is>
+      </c>
+      <c r="P58" s="4" t="inlineStr"/>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-055</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Front Desk On</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Nurse nav shows billing + nurse station</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Toggle ON. Refresh session after settings save.</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>App shell nav</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>1. Sign in as nurse (or hard refresh).
+2. Inspect sidebar.</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Nurse station still listed. Billing, collections, reports visible (module flags permitting). Dedicated receptionist nav unchanged.</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr"/>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M59" s="4" t="inlineStr"/>
+      <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>app-shell.tsx</t>
+        </is>
+      </c>
+      <c r="P59" s="4" t="inlineStr"/>
+    </row>
+    <row r="60" ht="60" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>TS-10-056</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Front Desk Off</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Turning toggle off hides nurse billing nav and blocks manage</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>After TS-10-054. Superadmin sets nurseAsReceptionist false.</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>1. Save toggle off.
+2. Refresh nurse session.
+3. Retry cancel.</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>Billing nav gone. Cancel/reschedule 403 again. Existing visits unchanged.</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr"/>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M60" s="4" t="inlineStr"/>
+      <c r="N60" s="4" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>nav + APIs</t>
+        </is>
+      </c>
+      <c r="P60" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P56"/>
+  <autoFilter ref="A4:P60"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L77" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L81" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16643,7 +17990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -16674,7 +18021,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 28 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 30 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -16788,7 +18135,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nurseAsReceptionist false (default).</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -16808,7 +18155,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Billing roles ok. Nurse redirected/denied.</t>
+          <t>Receptionist, accountant, doctor ok. Nurse redirected/denied (see TS-14-029 when toggle on).</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr"/>
@@ -18161,7 +19508,7 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Nurse cannot PATCH pay</t>
+          <t>Nurse cannot PATCH pay when receptionist toggle is off</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -18176,7 +19523,7 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>ISSUED invoice.</t>
+          <t>ISSUED invoice. nurseAsReceptionist false.</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
@@ -18610,14 +19957,147 @@
       </c>
       <c r="P32" s="4" t="inlineStr"/>
     </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>TS-14-029</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist On</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Nurse can collect OPD and open invoices when toggle is on</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist true. Unpaid walk-in. Refresh nurse session.</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>CASH amount=due</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>1. Open /billing.
+2. Collect on /billing/collect/[id].</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>Billing pages load. Collect succeeds. Invoice PAID. Nurse still cannot approve waivers (TS-15) — only request if UI shows request.</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>POST collect + /billing</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>TS-14-030</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist On</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Nurse cannot approve waiver even with front-desk access</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Toggle ON. PENDING waiver.</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>waiver-decide</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>1. Try approve/reject waiver.</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>403 — WAIVER_APPROVER_ROLES remain SUPER_ADMIN + ACCOUNTANT only.</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr"/>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr"/>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>PATCH waiver-decide</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P32"/>
+  <autoFilter ref="A4:P34"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20753,7 +22233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P26"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -20784,7 +22264,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 22 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 23 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -21874,7 +23354,7 @@
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Nurse cannot open reports</t>
+          <t>Nurse cannot open reports when receptionist toggle is off</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -21889,7 +23369,7 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>nurseAsReceptionist false.</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -22323,14 +23803,81 @@
       </c>
       <c r="P26" s="4" t="inlineStr"/>
     </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TS-16-023</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Nurse Receptionist On</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Nurse can open collections and reports when toggle is on</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist true. Payments exist.</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>/billing/collections /billing/reports</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>1. Open both pages.
+2. Optional: send WhatsApp receipt if phone valid.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>Pages load with H1 data. Send allowed for billing roles including opted-in nurse.</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>/billing/collections + reports + send</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P26"/>
+  <autoFilter ref="A4:P27"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -22344,7 +23891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -22786,14 +24333,14 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>Create in TS-06</t>
+          <t>Create in TS-06. Front desk only if nurseAsReceptionist ON</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>U-H1-REC</t>
+          <t>U-H1-NUR2</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -22803,7 +24350,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>RECEPTIONIST</t>
+          <t>NURSE</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -22813,29 +24360,29 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>9876500013</t>
+          <t>9876500016</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Recep@123</t>
+          <t>Nurse2@123</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>rec@apexcare.test</t>
+          <t>nurse2@apexcare.test</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Create in TS-06</t>
+          <t>Second nurse — TS-07/TS-09 multiple-nurse receptionist</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>U-H1-ACC</t>
+          <t>U-H1-REC</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -22845,7 +24392,7 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>ACCOUNTANT</t>
+          <t>RECEPTIONIST</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -22855,62 +24402,104 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>9876500014</t>
+          <t>9876500013</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Account@123</t>
+          <t>Recep@123</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>acc@apexcare.test</t>
+          <t>rec@apexcare.test</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>Create in TS-06</t>
+          <t>Create in TS-06. Dedicated receptionist remains available with or without the nurse toggle</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>U-H1-ACC</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>ACCOUNTANT</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>(auto)</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>9876500014</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Account@123</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>acc@apexcare.test</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Create in TS-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>U-H4-SUPER</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>H4</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>SUPER_ADMIN</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>tenantbadmin</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>9876502002</t>
         </is>
       </c>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>TenantB@123</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>admin@tenantb.test</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>Second tenant — TS-20</t>
         </is>
@@ -23476,6 +25065,23 @@
       <c r="C47" s="4" t="inlineStr">
         <is>
           <t>Required when method=CARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>nurseAsReceptionist</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>false (default)</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>Hospital settings. Off: nurses stay clinical-only. On: every nurse gets receptionist front desk (register, queue, billing). Dedicated RECEPTIONIST still allowed.</t>
         </is>
       </c>
     </row>
@@ -27744,7 +29350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -27775,7 +29381,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 30 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 32 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -28006,7 +29612,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>NURSE: vitals Y, billing N, certificates N</t>
+          <t>NURSE default: vitals Y, billing N, certificates N, front desk N</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -28021,19 +29627,19 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
+          <t>nurseAsReceptionist false.</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>NURSE</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>NURSE</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>1. Probe.</t>
@@ -28041,7 +29647,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Vitals/nurse Y. Billing N. Cert issue N.</t>
+          <t>Vitals/nurse Y. Billing N. Cert issue N. Patient register/edit N. Queue manage N. See TS-20-031 when toggle on.</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr"/>
@@ -29781,7 +31387,7 @@
       </c>
       <c r="P33" s="4" t="inlineStr"/>
     </row>
-    <row r="34" ht="60" customHeight="1">
+    <row r="34" ht="162" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
           <t>TS-20-030</t>
@@ -29789,12 +31395,12 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Summary Matrix Sign-off</t>
+          <t>Matrix Nurse Receptionist</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Attach completed RBAC checklist to run</t>
+          <t>Toggle ON: nurse gets receptionist front desk, still not admin/doctor</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -29804,32 +31410,40 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>RBAC</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>TS-20-001..029 done.</t>
+          <t>nurseAsReceptionist true.</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Tester</t>
+          <t>NURSE</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>Checklist</t>
+          <t>Probe patients, billing, users, settings, assessment, certificates, vitals</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>1. Mark suite Pass only if no unexpected allows.</t>
+          <t>1. Register/edit patient Y.
+2. Queue/appointments manage Y.
+3. Billing collect Y.
+4. /hospital/users N.
+5. /hospital/settings N.
+6. Assessment approve N.
+7. Certificate issue N.
+8. Vitals Y.
+9. Waiver decide N.</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>Sign-off in Index notes.</t>
+          <t>Front desk Y. Clinical nurse duties stay. Superadmin/doctor-only actions stay denied.</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr"/>
@@ -29842,19 +31456,151 @@
       <c r="N34" s="4" t="inlineStr"/>
       <c r="O34" s="4" t="inlineStr">
         <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>TS-20-031</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Matrix Receptionist Unchanged</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Dedicated receptionist still has front desk when nurse toggle is on</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Toggle ON. U-H1-REC exists.</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>RECEPTIONIST</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Same probes as TS-20-001</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>1. Repeat receptionist matrix.</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>Patients/appointments/billing Y. Users/settings/assess/vitals N. Toggle does not remove the Receptionist role.</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>multi</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>TS-20-032</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Summary Matrix Sign-off</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Attach completed RBAC checklist to run</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>TS-20-001..031 done.</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Tester</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Checklist</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>1. Mark suite Pass only if no unexpected allows.</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>Sign-off in Index notes.</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
           <t>Index</t>
         </is>
       </c>
-      <c r="P34" s="4" t="inlineStr"/>
+      <c r="P36" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P34"/>
+  <autoFilter ref="A4:P36"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29868,7 +31614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -30141,6 +31887,29 @@
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>W-11</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>RBAC</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Nurses as receptionists is hospital-wide (all nurses), not per-nurse. Dedicated RECEPTIONIST role is still available.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>TS-07/TS-20</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30336,7 +32105,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>/api/hospital/settings, /api/hospital/doctor-profile, /api/hospital/staff/[id]/availability, /api/session/view-mode</t>
+          <t>/api/hospital/settings (branding, walk-in, nurseAsReceptionist), /api/hospital/doctor-profile, /api/hospital/staff/[id]/availability, /api/session/view-mode</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -31439,7 +33208,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -31578,12 +33347,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Browser</t>
+          <t>WHATSAPP_SUBSCRIPTION_BILL_TEMPLATE</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Chrome latest + one mobile viewport check</t>
+          <t>subscription_bill — UTILITY + Document header; sent to hospital SUPER_ADMIN on Razorpay renewal</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr"/>
@@ -31592,12 +33361,12 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Roles available in env</t>
+          <t>Browser</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SOFTWARE_ADMIN exists (9999999999) or create</t>
+          <t>Chrome latest + one mobile viewport check</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr"/>
@@ -31606,12 +33375,12 @@
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Out of scope modules</t>
+          <t>Roles available in env</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Do NOT execute Lab / Pharmacy / Ward scenarios</t>
+          <t>SOFTWARE_ADMIN exists (9999999999) or create</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr"/>
@@ -31620,16 +33389,30 @@
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Seed (optional)</t>
+          <t>Out of scope modules</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>prisma seed-demo-data — Demo@123 for demo hospitals</t>
+          <t>Do NOT execute Lab / Pharmacy / Ward scenarios</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr"/>
       <c r="D14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Seed (optional)</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>prisma seed-demo-data — Demo@123 for demo hospitals</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr"/>
+      <c r="D15" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -37136,7 +38919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -37167,7 +38950,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 20 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 23 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -37880,7 +39663,7 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Checkout success from TS-04-009.</t>
+          <t>Checkout success from TS-04-009. SUPER_ADMIN has a valid mobile.</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -37900,7 +39683,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>HospitalSubscription ACTIVE. Platform invoice PAID. Access restored if previously expired.</t>
+          <t>HospitalSubscription ACTIVE. Platform invoice PAID. Access restored if previously expired. First successful charge also WhatsApps subscription_bill to SUPER_ADMIN (same path as monthly renewal; webhook dedupes if it fires too).</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -38144,7 +39927,7 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Webhook secret set. Known subscription.</t>
+          <t>Webhook secret set. Known subscription. Hospital SUPER_ADMIN has a 10-digit mobile.</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -38164,7 +39947,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>First: invoice created. Second: no duplicate invoice (dedupe).</t>
+          <t>First: PAID platform invoice created + subscription_bill WhatsApp to SUPER_ADMIN. Second: no duplicate invoice and no second WhatsApp (dedupe by razorpayPaymentId).</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr"/>
@@ -38578,14 +40361,215 @@
       </c>
       <c r="P24" s="4" t="inlineStr"/>
     </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>TS-04-021</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Renewal Bill</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Successful monthly renewal WhatsApps subscription bill to SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>AskEva/WhatsApp configured or console fallback. SaaS billing settings filled. Hospital SUPER_ADMIN mobile valid. Active Razorpay subscription.</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Event subscription.charged on the renewal date. Template subscription_bill.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>1. Wait for / simulate successful Razorpay subscription.charged.
+2. Confirm PlatformInvoice PAID.
+3. Check OutboundMessage + WhatsApp on SUPER_ADMIN mobile.</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>PDF uses SaaS billing-settings company name/address/GSTIN/bank/terms. Template vars: admin_name, hospital_name, invoice_no, total_amount, billing_period. Recipient is hospital SUPER_ADMIN only — not receptionist, not a doctor-only user. Audit SUBSCRIPTION_BILL_SENT. Charge stays PAID if WhatsApp fails (SUBSCRIPTION_BILL_FAILED).</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>recordSubscriptionCharge → notifySubscriptionRenewalBill</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>TS-04-022</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Renewal Bill</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Doctor-as-admin still receives the monthly bill on SUPER_ADMIN mobile</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Hospital SUPER_ADMIN also practices as doctor (admin-as-doctor). Same user mobile.</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN mobile (doctor-admin).</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>1. Renew subscription successfully.
+2. Confirm WhatsApp destination.</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>Bill goes to that SUPER_ADMIN number (the doctor-admin). Not a different DOCTOR user. One SUPER_ADMIN per hospital.</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>platform-invoice-whatsapp.ts</t>
+        </is>
+      </c>
+      <c r="P26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>TS-04-023</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Renewal Bill</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Missing SUPER_ADMIN mobile skips WhatsApp; invoice still PAID</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Hospital SUPER_ADMIN mobile blank/invalid.</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>System</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>subscription.charged</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>1. Charge subscription.</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>PlatformInvoice PAID. WhatsApp skipped. Audit SUBSCRIPTION_BILL_SKIPPED. Hospital access not blocked.</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>notifySubscriptionRenewalBill</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P24"/>
+  <autoFilter ref="A4:P27"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -38599,7 +40583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -38630,7 +40614,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 24 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 25 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -39360,19 +41344,19 @@
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>companyName, gstin, invoicePrefix</t>
+          <t>companyName, gstin, invoicePrefix, address, bank, terms</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>1. Open /platform/billing-settings.
-2. Update prefix.
+2. Update company details + prefix.
 3. Save.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Settings persist. New platform invoices use new prefix.</t>
+          <t>Settings persist. New subscription invoices use new prefix. Page copy states these details print on every subscription bill WhatsApped to hospital SUPER_ADMIN.</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr"/>
@@ -39438,7 +41422,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Shows invoiceNo, hospital, status, lines, total.</t>
+          <t>Shows invoiceNo, hospital, status, lines, total, plus SaaS company name/address/GSTIN/bank/terms from billing settings.</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr"/>
@@ -40317,14 +42301,82 @@
       </c>
       <c r="P28" s="4" t="inlineStr"/>
     </row>
+    <row r="29" ht="60" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>TS-05-025</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Billing Settings</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>SaaS billing details appear on monthly subscription WhatsApp PDF</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Billing settings saved (company name, address, phone, email, GSTIN, bank, terms). Hospital SUPER_ADMIN mobile valid. WhatsApp template subscription_bill approved in AskEva.</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>SOFTWARE_ADMIN</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Renewal from TS-04-021</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>1. Confirm billing settings.
+2. Trigger successful subscription.charged.
+3. Open WhatsApp PDF on SUPER_ADMIN phone and /platform/invoices/[id].</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>PDF letterhead matches billing settings. Bill-to is the hospital. Amount/period match the charge. Recipient is SUPER_ADMIN (doctor-admin uses the same number). Company phone on the form is seller contact, not the WhatsApp destination.</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>platform-invoice-pdf.ts + subscription_bill</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P28"/>
+  <autoFilter ref="A4:P29"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
@@ -40338,7 +42390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40369,7 +42421,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 34 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 36 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -42718,14 +44770,147 @@
       </c>
       <c r="P38" s="4" t="inlineStr"/>
     </row>
+    <row r="39" ht="60" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>TS-06-035</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Receptionist and Nurse both remain selectable</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN on /hospital/users.</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Roles: Receptionist, Nurse</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>1. Open Add hospital user.
+2. Open Role dropdown.</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Receptionist and Nurse are both listed. Helper text: keep a dedicated receptionist, or turn on Nurses as receptionists in Hospital settings. Multiple nurses can share front-desk work.</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>/hospital/users</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40" ht="60" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>TS-06-036</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Roles</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Create a second NURSE (multiple nurses allowed)</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Seats available. U-H1-NUR exists.</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>U-H1-NUR2 mobile 9876500016 password Nurse2@123</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>1. Create another NURSE user.</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Second nurse created. Both nurses keep role NURSE (not converted to RECEPTIONIST). Front desk for both depends on the hospital toggle (TS-07-030).</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr"/>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/hospital/users</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P38"/>
+  <autoFilter ref="A4:P40"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L59" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L61" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/test-suite/MedERP_Test_Suite_updated.xlsx
+++ b/docs/test-suite/MedERP_Test_Suite_updated.xlsx
@@ -36,7 +36,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TS-01'!$A$4:$P$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TS-02'!$A$4:$P$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'TS-02'!$A$4:$P$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'TS-03'!$A$4:$P$22</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'TS-04'!$A$4:$P$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'TS-05'!$A$4:$P$29</definedName>
@@ -681,11 +681,11 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>Login, OTP, forgot/reset password, logout, rate limits, session</t>
+          <t>Login, OTP, forgot/reset password, logout, rate limits, 2-device 48h idle session</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>30 cases written</t>
+          <t>33 cases written</t>
         </is>
       </c>
     </row>
@@ -24877,7 +24877,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>7 days, httpOnly, SameSite=strict</t>
+          <t>48h idle sliding, max 2 devices, httpOnly, SameSite=strict</t>
         </is>
       </c>
     </row>
@@ -35443,7 +35443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -35474,7 +35474,7 @@
     <row r="2" ht="35" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Manual script — 30 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
+          <t>Manual script — 33 cases. Execute in Case ID order where dependencies exist. Update Status / Actual Result / Defect ID columns. Out of scope: Lab, Pharmacy, Wards.</t>
         </is>
       </c>
     </row>
@@ -35676,7 +35676,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>200 {ok, role:SUPER_ADMIN, sessionToken, redirectTo:'/'}. Cookie mederp_session set (7d, httpOnly, SameSite=strict). Lands on /. Audit LOGIN.</t>
+          <t>200 {ok, role:SUPER_ADMIN, sessionToken, redirectTo:'/'}. Cookie mederp_session set (48h idle, httpOnly, SameSite=strict). Lands on /. Audit LOGIN.</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr"/>
@@ -36910,7 +36910,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Expired session is rejected and deleted</t>
+          <t>Idle session &gt;48h is rejected and deleted</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -36925,7 +36925,7 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Create session with expiresAt in past (DB) or wait 7 days.</t>
+          <t>Create session with expiresAt in past (DB) or wait 48h with no activity.</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -36945,7 +36945,7 @@
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Treated as logged out. Session row deleted. Redirect /login.</t>
+          <t>Treated as logged out. Session row deleted. Cookie cleared. Redirect /login.</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr"/>
@@ -37559,14 +37559,215 @@
       </c>
       <c r="P34" s="4" t="inlineStr"/>
     </row>
+    <row r="35" ht="60" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>TS-02-031</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Session Cap</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Third login evicts the least-recently-used session</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Same user signed in on two devices.</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>SUPER_ADMIN</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Device A idle, Device B recently used, Device C new login</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>1. Login on A.
+2. Login on B (use B).
+3. Login on C.</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>C succeeds. A session row deleted (LRU). B still valid. Max 2 AppSession rows. A next request → login.</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>createSession extraSessionIds</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36" ht="60" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>TS-02-032</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Session Slide</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Activity within 48h does not require re-login</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Logged in. Use the app (page load or ping) before 48h idle.</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/session/ping while tab visible</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>1. Stay signed in and use the app / wait 15 min with tab visible.
+2. Continue working past 48h from original login.</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>lastSeenAt and expiresAt slide (throttle 5 min). Cookie re-issued. No login screen.</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr"/>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>GET/POST /api/session/ping + session-user</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37" ht="60" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>TS-02-033</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Session Idle</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>More than 48h idle requires sign-in</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Last activity &gt;48h ago.</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Stale session</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>1. Open any protected page.</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Must sign in again. AppShell/ping clear the cookie to avoid a login redirect loop.</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>Not Run</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr"/>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>AppShell + /api/session/ping</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:P34"/>
+  <autoFilter ref="A4:P37"/>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
     <mergeCell ref="A2:P2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="L5:L55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
+    <dataValidation sqref="L5:L58" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid Status" error="Pick a status" type="list">
       <formula1>"Not Run,Pass,Fail,Blocked,Skip"</formula1>
     </dataValidation>
   </dataValidations>
